--- a/tables_figures/final-tables_figures/Tables_LakeErie.xlsx
+++ b/tables_figures/final-tables_figures/Tables_LakeErie.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trentu-my.sharepoint.com/personal/sandraklemet_trentu_ca/Documents/Documents/Etudes/Trent/Xenopoulos lab/Projects/LakeErie_animal-excretion/tables_figures/final-tables_figures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{046A001F-BE88-4028-A1F8-A9829B7EE410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64951508-FA84-440C-A8BD-089B4B1E085B}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{046A001F-BE88-4028-A1F8-A9829B7EE410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{357FD79F-8688-43FA-9DCF-BDAE90B99C91}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E10462F-BD6C-49F1-8394-5EAC03425A95}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{7E10462F-BD6C-49F1-8394-5EAC03425A95}"/>
   </bookViews>
   <sheets>
     <sheet name="Table S1" sheetId="1" r:id="rId1"/>
-    <sheet name="Table S2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="5" r:id="rId3"/>
-    <sheet name="Table S7" sheetId="4" r:id="rId4"/>
-    <sheet name="Table S8" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
+    <sheet name="Table S7" sheetId="4" r:id="rId3"/>
+    <sheet name="Table S8" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="91">
   <si>
     <t>n</t>
   </si>
@@ -162,36 +161,9 @@
     <t>374.87 ± 284.71</t>
   </si>
   <si>
-    <t>Population N:P excretion (molar)</t>
-  </si>
-  <si>
-    <t>Biomass (g)</t>
-  </si>
-  <si>
-    <t>Lakewide</t>
-  </si>
-  <si>
-    <t>Western basin</t>
-  </si>
-  <si>
     <t>Dreissenids</t>
   </si>
   <si>
-    <t>1.57 ± 2.86</t>
-  </si>
-  <si>
-    <t>0.38 ± 0.66</t>
-  </si>
-  <si>
-    <t>0.28 ± 2.86</t>
-  </si>
-  <si>
-    <t>TDN</t>
-  </si>
-  <si>
-    <t>TDP</t>
-  </si>
-  <si>
     <t>Source</t>
   </si>
   <si>
@@ -204,24 +176,6 @@
     <t>P load (tonnes/yr)</t>
   </si>
   <si>
-    <t>Total TP</t>
-  </si>
-  <si>
-    <t>Total SRP</t>
-  </si>
-  <si>
-    <t>Tributary TP</t>
-  </si>
-  <si>
-    <t>Tributary SRP</t>
-  </si>
-  <si>
-    <t>Fish SRP</t>
-  </si>
-  <si>
-    <t>Dreissenids SRP</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -246,69 +200,6 @@
     <t>Mass-specifc N:P excr  ~  (1|Species)</t>
   </si>
   <si>
-    <r>
-      <t>Population N excretion (µg N/m</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2/h</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Population P excretion (µg P/m2/h)</t>
-  </si>
-  <si>
-    <t>Population N excretion (µg N/m2/h)</t>
-  </si>
-  <si>
-    <t>30486.244290020866</t>
-  </si>
-  <si>
-    <t>1807.116109548215</t>
-  </si>
-  <si>
-    <t>625.1164834324188</t>
-  </si>
-  <si>
-    <t>139.43545523175277</t>
-  </si>
-  <si>
-    <t>Turnover time (min)</t>
-  </si>
-  <si>
-    <t>Fish TDN</t>
-  </si>
-  <si>
-    <t>Fish TDP</t>
-  </si>
-  <si>
-    <t>Dreissenid TDN</t>
-  </si>
-  <si>
-    <t>Dreissenid TDP</t>
-  </si>
-  <si>
-    <t>Turnover time (h)</t>
-  </si>
-  <si>
-    <t>0.08 ± 0.13</t>
-  </si>
-  <si>
     <t>Chemical form</t>
   </si>
   <si>
@@ -328,18 +219,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tributary </t>
-  </si>
-  <si>
-    <t>949.67 ± 409.93</t>
-  </si>
-  <si>
-    <t>168.2 ± 72.61</t>
-  </si>
-  <si>
-    <t>29.08 ± 12.55</t>
-  </si>
-  <si>
-    <t>8.72 ± 3.77</t>
   </si>
   <si>
     <t>Tissue C:N (molar)</t>
@@ -524,6 +403,85 @@
   <si>
     <t>3.87 ± 0.63</t>
   </si>
+  <si>
+    <t>Lake-wide</t>
+  </si>
+  <si>
+    <t>Western Basin</t>
+  </si>
+  <si>
+    <t>Biomass (g m-2)</t>
+  </si>
+  <si>
+    <r>
+      <t>NH4</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>and SRP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">410.07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>± 54.39</t>
+    </r>
+  </si>
+  <si>
+    <t>147.83 ± 27.90</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">623.02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>± 117.59</t>
+    </r>
+  </si>
+  <si>
+    <t>85.32 ± 12.13</t>
+  </si>
+  <si>
+    <t>36053.22</t>
+  </si>
+  <si>
+    <t>203553.2</t>
+  </si>
+  <si>
+    <t>19388.61 ± 8685.34</t>
+  </si>
+  <si>
+    <t>3434.1 ± 1538.5</t>
+  </si>
 </sst>
 </file>
 
@@ -532,7 +490,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -572,6 +530,25 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -614,7 +591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -634,16 +611,12 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -651,7 +624,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -662,25 +634,17 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1000,27 +964,27 @@
   <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="8.7265625" style="9"/>
-    <col min="3" max="3" width="16.6328125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="9"/>
-    <col min="5" max="5" width="16.7265625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="9.90625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.26953125" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7265625" style="9"/>
+    <col min="1" max="2" width="8.7265625" style="8"/>
+    <col min="3" max="3" width="16.6328125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="8"/>
+    <col min="5" max="5" width="16.7265625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" style="8"/>
     <col min="9" max="9" width="12.36328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>104</v>
+      <c r="B1" s="14" t="s">
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1039,34 +1003,34 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>105</v>
+      <c r="B2" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="11">
         <v>31</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="16">
         <v>5.3666863354037204</v>
       </c>
-      <c r="G2" s="19">
+      <c r="G2" s="16">
         <v>66.967875000000006</v>
       </c>
       <c r="H2" s="6">
         <v>0.71456057920008187</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <v>17.9449837115917</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="9">
         <v>12.822777954691</v>
       </c>
       <c r="K2">
@@ -1078,25 +1042,25 @@
       <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="11">
         <v>31</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="16">
         <v>0.23005902777777701</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="16">
         <v>8.6622173075000006</v>
       </c>
       <c r="H3" s="6">
         <v>0.73220274080990966</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <v>3.15843739863096</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="9">
         <v>2.3126165199541102</v>
       </c>
       <c r="K3">
@@ -1108,25 +1072,25 @@
       <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="11">
         <v>31</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="16">
         <v>0.70305961972039699</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="16">
         <v>44.871254504088903</v>
       </c>
       <c r="H4" s="6">
         <v>1.6531409859487542</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>5.0647999507477701</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>8.3728283842123705</v>
       </c>
       <c r="K4">
@@ -1138,7 +1102,7 @@
       <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="11">
         <v>31</v>
       </c>
       <c r="E5" s="6" t="s">
@@ -1153,10 +1117,10 @@
       <c r="H5" s="6">
         <v>0.75948268036884348</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="9">
         <v>374.87096774193498</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="9">
         <v>284.70800737310702</v>
       </c>
       <c r="K5">
@@ -1168,11 +1132,11 @@
       <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="11">
         <v>12</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="F6" s="6">
         <v>11.34382714</v>
@@ -1183,10 +1147,10 @@
       <c r="H6" s="6">
         <v>5.3438688420760674E-2</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <v>12.6371983766666</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <v>0.67531530656202898</v>
       </c>
       <c r="K6">
@@ -1198,11 +1162,11 @@
       <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="11">
         <v>12</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>108</v>
+      <c r="E7" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="F7" s="6">
         <v>-24.14537322</v>
@@ -1213,10 +1177,10 @@
       <c r="H7" s="6">
         <v>-1.2453656847565353E-2</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <v>-23.6774790806666</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <v>0.29487119948602902</v>
       </c>
       <c r="K7">
@@ -1228,11 +1192,11 @@
       <c r="C8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="11">
         <v>12</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="F8" s="6">
         <v>44.849519899999997</v>
@@ -1243,10 +1207,10 @@
       <c r="H8" s="6">
         <v>3.7694815751541856E-2</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="9">
         <v>48.6443014926666</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="9">
         <v>1.83363798212852</v>
       </c>
       <c r="K8">
@@ -1258,11 +1222,11 @@
       <c r="C9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="11">
         <v>12</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="F9" s="6">
         <v>11.13641949</v>
@@ -1273,10 +1237,10 @@
       <c r="H9" s="6">
         <v>8.1201058351613065E-2</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <v>13.20763882</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <v>1.0724742505098499</v>
       </c>
       <c r="K9">
@@ -1285,14 +1249,14 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C10" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" s="13">
+      <c r="C10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="11">
         <v>12</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="F10" s="6">
         <v>3.2911418160000001</v>
@@ -1303,10 +1267,10 @@
       <c r="H10" s="6">
         <v>0.16359198384849752</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <v>3.8683595882000001</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="9">
         <v>0.63283261927299495</v>
       </c>
       <c r="K10">
@@ -1315,8 +1279,8 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>44</v>
+      <c r="A11" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>7</v>
@@ -1336,10 +1300,10 @@
       <c r="H11" s="6">
         <v>0.8446738818699121</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="9">
         <v>108.857118772098</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="9">
         <v>91.948765082402105</v>
       </c>
       <c r="K11">
@@ -1366,10 +1330,10 @@
       <c r="H12" s="6">
         <v>1.3628137102538971</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="9">
         <v>19.280703668212499</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="9">
         <v>26.276007302382599</v>
       </c>
       <c r="K12">
@@ -1396,10 +1360,10 @@
       <c r="H13" s="6">
         <v>0.53331537144886365</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="9">
         <v>3.3337677352144102</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="9">
         <v>1.77794957803011</v>
       </c>
       <c r="K13">
@@ -1417,19 +1381,19 @@
       <c r="E14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="20">
         <v>4.6899999999999997E-3</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="16">
         <v>5.04E-2</v>
       </c>
       <c r="H14" s="6">
         <v>0.93566649507428845</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <v>2.0995079285714199E-2</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="9">
         <v>1.9644392249071E-2</v>
       </c>
       <c r="K14">
@@ -1447,19 +1411,19 @@
       <c r="E15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="16">
         <v>6.6874224030000002</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="16">
         <v>9.5257914939999999</v>
       </c>
       <c r="H15" s="6">
         <v>0.16145851006903911</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="9">
         <v>8.1493068864999998</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="9">
         <v>1.3157749479896499</v>
       </c>
       <c r="K15">
@@ -1474,22 +1438,22 @@
       <c r="D16" s="3">
         <v>6</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="16">
         <v>-25.891241690000001</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="16">
         <v>-23.65066719</v>
       </c>
       <c r="H16" s="6">
         <v>-3.9498419781143553E-2</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="9">
         <v>-24.796957509999999</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="9">
         <v>0.97944063702516004</v>
       </c>
       <c r="K16">
@@ -1507,19 +1471,19 @@
       <c r="E17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="16">
         <v>43.39079031</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="16">
         <v>47.416577259999997</v>
       </c>
       <c r="H17" s="6">
         <v>3.0201909095104857E-2</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <v>45.801451104999998</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="9">
         <v>1.3832912626970999</v>
       </c>
       <c r="K17">
@@ -1534,22 +1498,22 @@
       <c r="D18" s="3">
         <v>6</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="16">
         <v>10.2791689</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="16">
         <v>11.155228490000001</v>
       </c>
       <c r="H18" s="6">
         <v>2.7766480787994045E-2</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="9">
         <v>10.8646716866666</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="9">
         <v>0.30167369765569102</v>
       </c>
       <c r="K18">
@@ -1567,19 +1531,19 @@
       <c r="E19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="16">
         <v>1.098260748</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="16">
         <v>1.4162833269999999</v>
       </c>
       <c r="H19" s="6">
         <v>9.8735667071949806E-2</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="9">
         <v>1.2784571734999901</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="9">
         <v>0.12622932184844099</v>
       </c>
       <c r="K19">
@@ -1588,28 +1552,28 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C20" s="9" t="s">
-        <v>93</v>
+      <c r="C20" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="D20" s="3">
         <v>6</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F20" s="19">
+        <v>61</v>
+      </c>
+      <c r="F20" s="16">
         <v>4.7499695390000003</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="16">
         <v>5.0604236770000002</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="16">
         <v>2.2332734953806142E-2</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="9">
         <v>4.9192410378333298</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="9">
         <v>0.109860106271818</v>
       </c>
       <c r="K20">
@@ -1618,34 +1582,34 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>106</v>
+      <c r="B21" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="11">
         <v>102</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="16">
         <v>3.3479632499999998</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="16">
         <v>40.737754649999999</v>
       </c>
       <c r="H21" s="6">
         <v>0.53641309855540953</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="9">
         <v>12.1661420900188</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="9">
         <v>6.5260779759723704</v>
       </c>
       <c r="K21">
@@ -1657,25 +1621,25 @@
       <c r="C22" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="11">
         <v>102</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="16">
         <v>0.20891138715728699</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="16">
         <v>18.627624300000001</v>
       </c>
       <c r="H22" s="6">
         <v>1.3026258318854445</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="9">
         <v>3.2210867729442998</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="9">
         <v>4.1958708371817703</v>
       </c>
       <c r="K22">
@@ -1687,25 +1651,25 @@
       <c r="C23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="11">
         <v>102</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="16">
         <v>0.43780606729883498</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="16">
         <v>18.593047258004599</v>
       </c>
       <c r="H23" s="6">
         <v>0.93479773691793699</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="9">
         <v>5.1023960287145496</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="9">
         <v>4.7697082605014298</v>
       </c>
       <c r="K23">
@@ -1717,25 +1681,25 @@
       <c r="C24" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="11">
         <v>102</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="16">
         <v>1</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="16">
         <v>887</v>
       </c>
       <c r="H24" s="6">
         <v>1.3841147434379779</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="9">
         <v>150.843137254901</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="9">
         <v>208.78421022094699</v>
       </c>
       <c r="K24">
@@ -1747,25 +1711,25 @@
       <c r="C25" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="11">
         <v>55</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="16">
         <v>5.0072538150000003</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="16">
         <v>13.59</v>
       </c>
       <c r="H25" s="6">
         <v>0.17621448508944335</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="9">
         <v>9.2261850927999998</v>
       </c>
-      <c r="J25" s="10" t="s">
+      <c r="J25" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K25">
@@ -1777,25 +1741,25 @@
       <c r="C26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="11">
         <v>55</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="16">
         <v>-26.521341150000001</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="16">
         <v>-13.5</v>
       </c>
       <c r="H26" s="6">
         <v>-0.13713131337330131</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="9">
         <v>-19.134563428545398</v>
       </c>
-      <c r="J26" s="10" t="s">
+      <c r="J26" s="9" t="s">
         <v>29</v>
       </c>
       <c r="K26">
@@ -1807,25 +1771,25 @@
       <c r="C27" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="11">
         <v>55</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="16">
         <v>38.528017779999999</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="16">
         <v>52.43</v>
       </c>
       <c r="H27" s="6">
         <v>6.5573100201909276E-2</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="9">
         <v>45.962858123090903</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="9">
         <v>3.0139271012715798</v>
       </c>
       <c r="K27">
@@ -1837,25 +1801,25 @@
       <c r="C28" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="11">
         <v>55</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="16">
         <v>10.66434507</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="16">
         <v>16.329999999999998</v>
       </c>
       <c r="H28" s="6">
         <v>8.440206336813974E-2</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="9">
         <v>12.919240196000001</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J28" s="9">
         <v>1.09041052969101</v>
       </c>
       <c r="K28">
@@ -1864,30 +1828,30 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" s="15">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="13">
         <v>55</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F29" s="20">
+      <c r="E29" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" s="17">
         <v>3.21</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="17">
         <v>4.6851086640000004</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="17">
         <v>7.9429008703033405E-2</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="9">
         <v>3.5726964022908998</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="9">
         <v>0.28377573363086001</v>
       </c>
       <c r="K29">
@@ -1896,7 +1860,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1922,318 +1886,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57CD3C6F-D001-4806-B08E-514F56FFD6B0}">
-  <dimension ref="A1:J12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{671D37D4-6EF4-46EF-8C28-33AB8A23A2D1}">
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="18.54296875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="9">
-        <v>30</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="21">
-        <v>3.7046465985678898E-4</v>
-      </c>
-      <c r="F2" s="12">
-        <v>12.7504356569208</v>
-      </c>
-      <c r="G2" s="22">
-        <v>1.8170220224454101</v>
-      </c>
-      <c r="H2" s="10">
-        <v>1.5724927001907001</v>
-      </c>
-      <c r="I2" s="10">
-        <v>2.85725386638115</v>
-      </c>
-      <c r="J2" s="10">
-        <f>I2/H2</f>
-        <v>1.8170220224454101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9"/>
-      <c r="B3" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="9">
-        <v>30</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="21">
-        <v>5.6736503682944603E-5</v>
-      </c>
-      <c r="F3" s="12">
-        <v>2.82540222026664</v>
-      </c>
-      <c r="G3" s="22">
-        <v>1.7396606448036007</v>
-      </c>
-      <c r="H3" s="10">
-        <v>0.37753767361708301</v>
-      </c>
-      <c r="I3" s="10">
-        <v>0.65678743272234597</v>
-      </c>
-      <c r="J3" s="10">
-        <f t="shared" ref="J3:J9" si="0">I3/H3</f>
-        <v>1.7396606448036007</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="9"/>
-      <c r="B4" s="5" t="s">
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>0.101184725</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>2.98</v>
+      </c>
+      <c r="D3">
+        <v>2.7158151785024698</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="9">
-        <v>30</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="21">
-        <v>1.20147863494511E-4</v>
-      </c>
-      <c r="F4" s="12">
-        <v>1.32506092565571</v>
-      </c>
-      <c r="G4" s="12">
-        <v>1.4001791999784388</v>
-      </c>
-      <c r="H4" s="10">
-        <v>0.27858229244398403</v>
-      </c>
-      <c r="I4" s="10">
-        <v>0.39006513136237703</v>
-      </c>
-      <c r="J4" s="10">
-        <f t="shared" si="0"/>
-        <v>1.4001791999784388</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9"/>
-      <c r="B5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="9">
-        <v>30</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="21">
-        <v>2.15481499999999E-5</v>
-      </c>
-      <c r="F5" s="12">
-        <v>0.60090285449999903</v>
-      </c>
-      <c r="G5" s="12">
-        <v>1.6288872123251554</v>
-      </c>
-      <c r="H5" s="10">
-        <v>8.207906056E-2</v>
-      </c>
-      <c r="I5" s="10">
-        <v>0.13369753214584601</v>
-      </c>
-      <c r="J5" s="10">
-        <f t="shared" si="0"/>
-        <v>1.6288872123251554</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="9">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" s="12">
-        <v>491.368939022787</v>
-      </c>
-      <c r="F6" s="12">
-        <v>1776.4877022440301</v>
-      </c>
-      <c r="G6" s="12">
-        <v>0.43166192963429245</v>
-      </c>
-      <c r="H6" s="28">
-        <v>949.66496846584698</v>
-      </c>
-      <c r="I6" s="10">
-        <v>409.93421279405698</v>
-      </c>
-      <c r="J6" s="10">
-        <f t="shared" si="0"/>
-        <v>0.43166192963429245</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
-      <c r="B7" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="9">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" s="12">
-        <v>87.030954079326605</v>
-      </c>
-      <c r="F7" s="12">
-        <v>314.65037237390101</v>
-      </c>
-      <c r="G7" s="12">
-        <v>0.43166192963429351</v>
-      </c>
-      <c r="H7" s="28">
-        <v>168.20405544084099</v>
-      </c>
-      <c r="I7" s="10">
-        <v>72.607287143907101</v>
-      </c>
-      <c r="J7" s="10">
-        <f t="shared" si="0"/>
-        <v>0.43166192963429345</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9"/>
-      <c r="B8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="9">
-        <v>8</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" s="12">
-        <v>15.0482571418248</v>
-      </c>
-      <c r="F8" s="12">
-        <v>54.405237347365102</v>
-      </c>
-      <c r="G8" s="12">
-        <v>0.4316619296342904</v>
-      </c>
-      <c r="H8" s="28">
-        <v>29.083650815368799</v>
-      </c>
-      <c r="I8" s="10">
-        <v>12.554304831772001</v>
-      </c>
-      <c r="J8" s="10">
-        <f t="shared" si="0"/>
-        <v>0.43166192963429045</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="14"/>
-      <c r="B9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="14">
-        <v>8</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" s="16">
-        <v>4.5138888899999996</v>
-      </c>
-      <c r="F9" s="16">
-        <v>16.319444444999998</v>
-      </c>
-      <c r="G9" s="16">
-        <v>0.43166192963429162</v>
-      </c>
-      <c r="H9" s="28">
-        <v>8.7239583334374995</v>
-      </c>
-      <c r="I9" s="10">
-        <v>3.7658006882607902</v>
-      </c>
-      <c r="J9" s="10">
-        <f t="shared" si="0"/>
-        <v>0.43166192963429167</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4">
+        <v>8.3197674425999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <v>6.1913118284299999</v>
+      </c>
+      <c r="D5">
+        <v>36.508190363597798</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2241,104 +1951,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88943F4-F732-4600-AB61-2BDEB71283F0}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.7265625" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="12">
-        <f>H2/E2</f>
-        <v>0.66110752499385972</v>
-      </c>
-      <c r="C2" s="12">
-        <f>B2*60</f>
-        <v>39.666451499631584</v>
-      </c>
-      <c r="E2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2">
-        <v>413.26921119487099</v>
-      </c>
-      <c r="I2">
-        <v>13.429482113076901</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="12">
-        <f>I2/E3</f>
-        <v>9.6313251825054916E-2</v>
-      </c>
-      <c r="C3" s="12">
-        <f t="shared" ref="C3:C5" si="0">B3*60</f>
-        <v>5.778795109503295</v>
-      </c>
-      <c r="E3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="10"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="12">
-        <f>H2/E4</f>
-        <v>1.3555924018169343E-2</v>
-      </c>
-      <c r="C4" s="12">
-        <f t="shared" si="0"/>
-        <v>0.81335544109016056</v>
-      </c>
-      <c r="E4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="16">
-        <f>I2/E5</f>
-        <v>7.4314439687189508E-3</v>
-      </c>
-      <c r="C5" s="16">
-        <f t="shared" si="0"/>
-        <v>0.44588663812313706</v>
-      </c>
-      <c r="E5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="10"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57374BE3-3D12-4D5E-AD85-8268CE3AECB4}">
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2347,180 +1959,180 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>64</v>
+      <c r="A1" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="9">
+      <c r="A2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="8">
         <v>4</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>37</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <f>C2-MIN($C$2:$C$6)</f>
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" s="9">
+      <c r="A3" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="8">
         <v>4</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>38</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <f t="shared" ref="D3:D5" si="0">C3-MIN($C$2:$C$6)</f>
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="9">
+      <c r="A4" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="8">
         <v>4</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>37</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="9">
+      <c r="A5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="8">
         <v>4</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>35</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="9">
+      <c r="A6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="8">
         <v>3</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>30</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <f>C6-MIN($C$2:$C$6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="9">
+      <c r="A7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="8">
         <v>4</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>82</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <f>C7-MIN($C$7:$C$9)</f>
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" s="9">
+      <c r="A8" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="8">
         <v>4</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>82</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <f t="shared" ref="D8:D9" si="1">C8-MIN($C$7:$C$9)</f>
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="9">
+      <c r="A9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="8">
         <v>3</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>75</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="9">
+      <c r="A10" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="8">
         <v>4</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>66</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <f>C10-MIN($C$10:$C$12)</f>
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="9">
+      <c r="A11" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="8">
         <v>4</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>82</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <f t="shared" ref="D11:D12" si="2">C11-MIN($C$10:$C$12)</f>
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="14">
+      <c r="A12" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="12">
         <v>3</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="12">
         <v>59</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2530,227 +2142,222 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91EB70EB-667B-40AE-9B29-064778A65493}">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="11.453125" customWidth="1"/>
-    <col min="5" max="5" width="11.08984375" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" customWidth="1"/>
     <col min="6" max="6" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="17" t="s">
+    <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="11">
+        <v>13544</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="11">
+        <v>4470</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="11">
+        <v>3440</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="11">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="11">
+        <v>12591</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="11">
+        <v>3381</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="11">
+        <v>41900</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="11">
+        <v>3099</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="11">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="E11" s="16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="13">
-        <v>13544</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="13">
-        <v>4470</v>
-      </c>
-      <c r="P3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q3">
-        <v>413.26921119487099</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="13">
-        <v>12591</v>
-      </c>
-      <c r="P4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q4">
-        <v>13.429482113076901</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="13">
-        <v>3381</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="13">
-        <v>41900</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="13">
-        <v>3440</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="13">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="13">
-        <v>3099</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="13">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="19">
-        <v>1147.6570311615701</v>
-      </c>
-      <c r="E11" s="19">
-        <v>238.24310028683499</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="26">
-        <v>12439.757279077599</v>
-      </c>
-      <c r="E12" s="26">
-        <v>2951.7960619758001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="13">
-        <v>191142.316905477</v>
-      </c>
-      <c r="E13" s="13">
-        <v>33855.005646673999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="27">
-        <v>187862.429873307</v>
-      </c>
-      <c r="E14" s="27">
-        <v>33274.074140808298</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="D15" s="5"/>
     </row>
   </sheetData>

--- a/tables_figures/final-tables_figures/Tables_LakeErie.xlsx
+++ b/tables_figures/final-tables_figures/Tables_LakeErie.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trentu-my.sharepoint.com/personal/sandraklemet_trentu_ca/Documents/Documents/Etudes/Trent/Xenopoulos lab/Projects/LakeErie_animal-excretion/tables_figures/final-tables_figures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{046A001F-BE88-4028-A1F8-A9829B7EE410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{357FD79F-8688-43FA-9DCF-BDAE90B99C91}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="13_ncr:1_{046A001F-BE88-4028-A1F8-A9829B7EE410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{948FB8A8-95C0-483A-84E7-C240A045A22B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{7E10462F-BD6C-49F1-8394-5EAC03425A95}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{7E10462F-BD6C-49F1-8394-5EAC03425A95}"/>
   </bookViews>
   <sheets>
-    <sheet name="Table S1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
-    <sheet name="Table S7" sheetId="4" r:id="rId3"/>
-    <sheet name="Table S8" sheetId="3" r:id="rId4"/>
+    <sheet name="Table 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Table S4" sheetId="4" r:id="rId2"/>
+    <sheet name="Table S5" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="94">
   <si>
     <t>n</t>
   </si>
@@ -168,12 +167,6 @@
   </si>
   <si>
     <t>response</t>
-  </si>
-  <si>
-    <t>N load (tonnes/yr)</t>
-  </si>
-  <si>
-    <t>P load (tonnes/yr)</t>
   </si>
   <si>
     <t>-</t>
@@ -410,9 +403,6 @@
     <t>Western Basin</t>
   </si>
   <si>
-    <t>Biomass (g m-2)</t>
-  </si>
-  <si>
     <r>
       <t>NH4</t>
     </r>
@@ -437,50 +427,115 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">410.07 </t>
+    <t>147.83 ± 27.90</t>
+  </si>
+  <si>
+    <t>85.32 ± 12.13</t>
+  </si>
+  <si>
+    <t>36053.22</t>
+  </si>
+  <si>
+    <t>203553.2</t>
+  </si>
+  <si>
+    <t>19388.61 ± 8685.34</t>
+  </si>
+  <si>
+    <t>3434.1 ± 1538.5</t>
+  </si>
+  <si>
+    <r>
+      <t>Biomass (g m</t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
-      <t>± 54.39</t>
-    </r>
-  </si>
-  <si>
-    <t>147.83 ± 27.90</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">623.02 </t>
+      <t>-2</t>
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
-      <t>± 117.59</t>
-    </r>
-  </si>
-  <si>
-    <t>85.32 ± 12.13</t>
-  </si>
-  <si>
-    <t>36053.22</t>
-  </si>
-  <si>
-    <t>203553.2</t>
-  </si>
-  <si>
-    <t>19388.61 ± 8685.34</t>
-  </si>
-  <si>
-    <t>3434.1 ± 1538.5</t>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>P load (tonnes yr</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>N load (tonnes yr</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>8.32 ± 2.16</t>
+  </si>
+  <si>
+    <t>6.19 ± 2.77</t>
+  </si>
+  <si>
+    <t>410.07 ± 54.39</t>
+  </si>
+  <si>
+    <t>1.6 ± 0.3</t>
+  </si>
+  <si>
+    <t>623.02 ± 117.59</t>
   </si>
 </sst>
 </file>
@@ -545,10 +600,12 @@
       <family val="1"/>
     </font>
     <font>
+      <b/>
+      <vertAlign val="superscript"/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -644,7 +701,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -981,7 +1038,7 @@
         <v>9</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>42</v>
@@ -1007,7 +1064,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>7</v>
@@ -1136,7 +1193,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F6" s="6">
         <v>11.34382714</v>
@@ -1166,7 +1223,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F7" s="6">
         <v>-24.14537322</v>
@@ -1196,7 +1253,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F8" s="6">
         <v>44.849519899999997</v>
@@ -1226,7 +1283,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F9" s="6">
         <v>11.13641949</v>
@@ -1250,13 +1307,13 @@
     </row>
     <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C10" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" s="11">
         <v>12</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F10" s="6">
         <v>3.2911418160000001</v>
@@ -1553,13 +1610,13 @@
     </row>
     <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D20" s="3">
         <v>6</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F20" s="16">
         <v>4.7499695390000003</v>
@@ -1586,7 +1643,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>7</v>
@@ -1831,13 +1888,13 @@
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D29" s="13">
         <v>55</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F29" s="17">
         <v>3.21</v>
@@ -1886,71 +1943,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{671D37D4-6EF4-46EF-8C28-33AB8A23A2D1}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2">
-        <v>0.101184725</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3">
-        <v>2.98</v>
-      </c>
-      <c r="D3">
-        <v>2.7158151785024698</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4">
-        <v>8.3197674425999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5">
-        <v>6.1913118284299999</v>
-      </c>
-      <c r="D5">
-        <v>36.508190363597798</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57374BE3-3D12-4D5E-AD85-8268CE3AECB4}">
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1960,21 +1952,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="D1" s="19" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B2" s="8">
         <v>4</v>
@@ -1989,7 +1981,7 @@
     </row>
     <row r="3" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B3" s="8">
         <v>4</v>
@@ -2004,7 +1996,7 @@
     </row>
     <row r="4" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B4" s="8">
         <v>4</v>
@@ -2019,7 +2011,7 @@
     </row>
     <row r="5" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B5" s="8">
         <v>4</v>
@@ -2034,7 +2026,7 @@
     </row>
     <row r="6" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B6" s="8">
         <v>3</v>
@@ -2049,7 +2041,7 @@
     </row>
     <row r="7" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B7" s="8">
         <v>4</v>
@@ -2064,7 +2056,7 @@
     </row>
     <row r="8" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B8" s="8">
         <v>4</v>
@@ -2079,7 +2071,7 @@
     </row>
     <row r="9" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" s="8">
         <v>3</v>
@@ -2094,7 +2086,7 @@
     </row>
     <row r="10" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B10" s="8">
         <v>4</v>
@@ -2109,7 +2101,7 @@
     </row>
     <row r="11" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B11" s="8">
         <v>4</v>
@@ -2124,7 +2116,7 @@
     </row>
     <row r="12" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B12" s="12">
         <v>3</v>
@@ -2142,223 +2134,249 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91EB70EB-667B-40AE-9B29-064778A65493}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="13.26953125" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="18.1796875" customWidth="1"/>
-    <col min="6" max="6" width="11.1796875" customWidth="1"/>
+    <col min="3" max="4" width="13.26953125" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="18.1796875" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>41</v>
       </c>
       <c r="B1" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="14" t="s">
+      <c r="C2" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="F2" s="11">
         <v>13544</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
       <c r="B3" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C3" s="8"/>
-      <c r="D3" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="11">
+      <c r="D3" s="8"/>
+      <c r="E3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="11">
         <v>4470</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="8"/>
       <c r="B4" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="11">
+        <v>78</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="11">
         <v>3440</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="8"/>
       <c r="B5" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5" s="8"/>
-      <c r="D5" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="11">
+      <c r="D5" s="8"/>
+      <c r="E5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="11">
         <v>860</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="11">
+        <v>77</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="11">
         <v>12591</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7" s="8"/>
-      <c r="D7" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="11">
+      <c r="D7" s="8"/>
+      <c r="E7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="11">
         <v>3381</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8"/>
       <c r="B8" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8" s="8"/>
-      <c r="D8" s="11">
+      <c r="D8" s="8"/>
+      <c r="E8" s="11">
         <v>41900</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F8" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8"/>
       <c r="B9" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="11">
+        <v>78</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="11">
         <v>3099</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="11">
+      <c r="D10" s="8"/>
+      <c r="E10" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="11">
         <v>713</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0.1</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B13" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" s="17" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="D15" s="5"/>
+      <c r="E14" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E15" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tables_figures/final-tables_figures/Tables_LakeErie.xlsx
+++ b/tables_figures/final-tables_figures/Tables_LakeErie.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trentu-my.sharepoint.com/personal/sandraklemet_trentu_ca/Documents/Documents/Etudes/Trent/Xenopoulos lab/Projects/LakeErie_animal-excretion/tables_figures/final-tables_figures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="13_ncr:1_{046A001F-BE88-4028-A1F8-A9829B7EE410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{948FB8A8-95C0-483A-84E7-C240A045A22B}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{046A001F-BE88-4028-A1F8-A9829B7EE410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEF72EE3-44B6-44D6-AB9C-BC0935FF94CA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{7E10462F-BD6C-49F1-8394-5EAC03425A95}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="94">
   <si>
     <t>n</t>
   </si>
@@ -2136,7 +2136,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91EB70EB-667B-40AE-9B29-064778A65493}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="4" width="13.26953125" customWidth="1"/>
@@ -2242,7 +2242,7 @@
         <v>43</v>
       </c>
       <c r="F6" s="11">
-        <v>12591</v>
+        <v>6153</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2256,7 +2256,7 @@
         <v>43</v>
       </c>
       <c r="F7" s="11">
-        <v>3381</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2267,7 +2267,7 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="11">
-        <v>41900</v>
+        <v>19488</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>43</v>
@@ -2286,7 +2286,7 @@
         <v>43</v>
       </c>
       <c r="F9" s="11">
-        <v>3099</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2300,83 +2300,97 @@
         <v>43</v>
       </c>
       <c r="F10" s="11">
-        <v>713</v>
+        <v>720</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="11">
+        <v>10330</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B12" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C12" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D12" s="11">
         <v>0.1</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E12" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F12" s="16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8" t="s">
+    <row r="13" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D13" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F13" s="22" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+    <row r="14" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B14" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D14" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F14" s="22" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12" t="s">
+    <row r="15" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D15" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E15" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F15" s="17" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="E15" s="5"/>
+    <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E16" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
